--- a/app/public/インボイス-パッキングリスト-本社用.xlsx
+++ b/app/public/インボイス-パッキングリスト-本社用.xlsx
@@ -1,30 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\masuda-vinyl-ops\app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948FE8B9-C7A1-4EF8-AD96-720F80407E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2391DE-2F63-4915-AF25-833875F99C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="798" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2724" yWindow="-25920" windowWidth="21600" windowHeight="25296" tabRatio="798" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOICE" sheetId="1" r:id="rId1"/>
     <sheet name="PACKING LIST" sheetId="2" r:id="rId2"/>
-    <sheet name="データ" sheetId="5" state="hidden" r:id="rId3"/>
+    <sheet name="INVOICE-20" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="PACKING LIST-20" sheetId="7" state="hidden" r:id="rId4"/>
+    <sheet name="データ" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INVOICE!$A$30:$J$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">データ!$A$2:$P$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'INVOICE-20'!$A$30:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">データ!$A$2:$P$107</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">INVOICE!$A$1:$K$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'INVOICE-20'!$A$1:$K$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'PACKING LIST'!$A$1:$K$63</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'PACKING LIST-20'!$A$1:$K$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="212">
   <si>
     <t>INVOICE</t>
     <phoneticPr fontId="4"/>
@@ -6590,6 +6595,2862 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867261AF-8980-4046-8438-A4795BA14B70}">
+  <dimension ref="A1:K60"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="32.75" customWidth="1"/>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="7.125" customWidth="1"/>
+    <col min="6" max="6" width="8.25" customWidth="1"/>
+    <col min="7" max="7" width="5.875" customWidth="1"/>
+    <col min="8" max="8" width="5.375" customWidth="1"/>
+    <col min="9" max="9" width="5.75" customWidth="1"/>
+    <col min="10" max="10" width="21.25" customWidth="1"/>
+    <col min="11" max="11" width="2.5" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="8.25" customHeight="1">
+      <c r="A1" s="176" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+    </row>
+    <row r="2" spans="1:11" ht="7.5" customHeight="1">
+      <c r="A2" s="176"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+    </row>
+    <row r="3" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A3" s="176"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="176"/>
+      <c r="I3" s="176"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="176"/>
+    </row>
+    <row r="4" spans="1:11" ht="4.5" customHeight="1">
+      <c r="A4" s="176"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="G5" s="224" t="s">
+        <v>207</v>
+      </c>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+    </row>
+    <row r="6" spans="1:11" ht="9.1999999999999993" customHeight="1"/>
+    <row r="7" spans="1:11" ht="10.5" customHeight="1" thickBot="1"/>
+    <row r="8" spans="1:11" ht="15">
+      <c r="A8" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="184" t="s">
+        <v>208</v>
+      </c>
+      <c r="H8" s="185"/>
+      <c r="I8" s="185"/>
+      <c r="J8" s="186"/>
+    </row>
+    <row r="9" spans="1:11" ht="5.45" customHeight="1">
+      <c r="A9" s="13"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="188"/>
+      <c r="I9" s="188"/>
+      <c r="J9" s="189"/>
+    </row>
+    <row r="10" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A10" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="187"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="188"/>
+      <c r="J10" s="189"/>
+    </row>
+    <row r="11" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A11" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="190" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="191"/>
+      <c r="I11" s="194" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="179"/>
+    </row>
+    <row r="12" spans="1:11" ht="15">
+      <c r="A12" s="73" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="193"/>
+      <c r="I12" s="195"/>
+      <c r="J12" s="196"/>
+    </row>
+    <row r="13" spans="1:11" ht="15">
+      <c r="A13" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="197" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="198"/>
+      <c r="I13" s="199" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="200"/>
+    </row>
+    <row r="14" spans="1:11" ht="15">
+      <c r="A14" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="177" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="178"/>
+      <c r="I14" s="178"/>
+      <c r="J14" s="179"/>
+    </row>
+    <row r="15" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A15" s="15"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="207" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="208"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="209"/>
+    </row>
+    <row r="16" spans="1:11" ht="15">
+      <c r="A16" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="182"/>
+      <c r="H16" s="210"/>
+      <c r="I16" s="210"/>
+      <c r="J16" s="211"/>
+    </row>
+    <row r="17" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+      <c r="A17" s="16"/>
+      <c r="B17" s="89"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="182"/>
+      <c r="H17" s="210"/>
+      <c r="I17" s="210"/>
+      <c r="J17" s="211"/>
+    </row>
+    <row r="18" spans="1:10" ht="6" customHeight="1">
+      <c r="A18" s="16"/>
+      <c r="B18" s="89"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="210"/>
+      <c r="I18" s="210"/>
+      <c r="J18" s="211"/>
+    </row>
+    <row r="19" spans="1:10" ht="18.75">
+      <c r="A19" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="212"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="213"/>
+      <c r="J19" s="214"/>
+    </row>
+    <row r="20" spans="1:10" ht="15">
+      <c r="A20" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="37"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" ht="15">
+      <c r="A21" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="5"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1">
+      <c r="A22" s="215" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="216"/>
+      <c r="C22" s="216"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="205"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1">
+      <c r="A23" s="215" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="216"/>
+      <c r="C23" s="216"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="205"/>
+      <c r="F23" s="206"/>
+      <c r="G23" s="81"/>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="6"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" ht="4.5" customHeight="1">
+      <c r="A24" s="35"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="226"/>
+      <c r="D24" s="226"/>
+      <c r="E24" s="226"/>
+      <c r="F24" s="8"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" ht="18.75">
+      <c r="A25" s="229" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="230"/>
+      <c r="C25" s="230"/>
+      <c r="D25" s="230"/>
+      <c r="E25" s="230"/>
+      <c r="F25" s="227" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" s="81"/>
+      <c r="H25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" ht="11.25" customHeight="1">
+      <c r="A26" s="231"/>
+      <c r="B26" s="232"/>
+      <c r="C26" s="232"/>
+      <c r="D26" s="232"/>
+      <c r="E26" s="232"/>
+      <c r="F26" s="227"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="102" t="s">
+        <v>123</v>
+      </c>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A27" s="233"/>
+      <c r="B27" s="234"/>
+      <c r="C27" s="234"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="227"/>
+      <c r="G27" s="81"/>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" ht="6" customHeight="1" thickBot="1">
+      <c r="A28" s="235"/>
+      <c r="B28" s="236"/>
+      <c r="C28" s="236"/>
+      <c r="D28" s="236"/>
+      <c r="E28" s="236"/>
+      <c r="F28" s="228"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="14.25" thickBot="1">
+      <c r="A29" s="13"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="217" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="237" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="181"/>
+      <c r="D30" s="238" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="170" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="220" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="180" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="181"/>
+      <c r="I30" s="220" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="221"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="218"/>
+      <c r="B31" s="210"/>
+      <c r="C31" s="183"/>
+      <c r="D31" s="239"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="222"/>
+      <c r="G31" s="182"/>
+      <c r="H31" s="183"/>
+      <c r="I31" s="222"/>
+      <c r="J31" s="223"/>
+    </row>
+    <row r="32" spans="1:10" ht="27.75" customHeight="1">
+      <c r="A32" s="219"/>
+      <c r="B32" s="210"/>
+      <c r="C32" s="183"/>
+      <c r="D32" s="239"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="222"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="183"/>
+      <c r="I32" s="222"/>
+      <c r="J32" s="223"/>
+    </row>
+    <row r="33" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A33" s="150"/>
+      <c r="B33" s="153" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="154"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="90" t="str">
+        <f>VLOOKUP(B33,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>m</v>
+      </c>
+      <c r="F33" s="126">
+        <v>4000</v>
+      </c>
+      <c r="G33" s="155">
+        <f>VLOOKUP(B33,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.61</v>
+      </c>
+      <c r="H33" s="155"/>
+      <c r="I33" s="151">
+        <f>IFERROR(G33*F33, "")</f>
+        <v>2440</v>
+      </c>
+      <c r="J33" s="152"/>
+    </row>
+    <row r="34" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A34" s="150"/>
+      <c r="B34" s="153" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="154"/>
+      <c r="D34" s="107"/>
+      <c r="E34" s="90" t="str">
+        <f>VLOOKUP(B34,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F34" s="126">
+        <v>11000</v>
+      </c>
+      <c r="G34" s="155">
+        <f>VLOOKUP(B34,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.223</v>
+      </c>
+      <c r="H34" s="155"/>
+      <c r="I34" s="151">
+        <f t="shared" ref="I34:I52" si="0">IFERROR(G34*F34, "")</f>
+        <v>2453</v>
+      </c>
+      <c r="J34" s="152"/>
+    </row>
+    <row r="35" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A35" s="150"/>
+      <c r="B35" s="153" t="s">
+        <v>184</v>
+      </c>
+      <c r="C35" s="154"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="90" t="str">
+        <f>VLOOKUP(B35,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F35" s="122">
+        <v>6000</v>
+      </c>
+      <c r="G35" s="155">
+        <f>VLOOKUP(B35,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="H35" s="155"/>
+      <c r="I35" s="151">
+        <f t="shared" si="0"/>
+        <v>1278</v>
+      </c>
+      <c r="J35" s="152"/>
+    </row>
+    <row r="36" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A36" s="148"/>
+      <c r="B36" s="153" t="s">
+        <v>185</v>
+      </c>
+      <c r="C36" s="154"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="90" t="str">
+        <f>VLOOKUP(B36,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F36" s="122">
+        <v>5000</v>
+      </c>
+      <c r="G36" s="155">
+        <f>VLOOKUP(B36,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.223</v>
+      </c>
+      <c r="H36" s="155"/>
+      <c r="I36" s="151">
+        <f t="shared" si="0"/>
+        <v>1115</v>
+      </c>
+      <c r="J36" s="152"/>
+    </row>
+    <row r="37" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A37" s="148"/>
+      <c r="B37" s="153" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="154"/>
+      <c r="D37" s="121"/>
+      <c r="E37" s="90" t="str">
+        <f>VLOOKUP(B37,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F37" s="123">
+        <v>11000</v>
+      </c>
+      <c r="G37" s="155">
+        <f>VLOOKUP(B37,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="H37" s="155"/>
+      <c r="I37" s="151">
+        <f t="shared" si="0"/>
+        <v>2585</v>
+      </c>
+      <c r="J37" s="152"/>
+    </row>
+    <row r="38" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A38" s="148"/>
+      <c r="B38" s="153" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="154"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="90" t="str">
+        <f>VLOOKUP(B38,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F38" s="122">
+        <v>5500</v>
+      </c>
+      <c r="G38" s="155">
+        <f>VLOOKUP(B38,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.224</v>
+      </c>
+      <c r="H38" s="155"/>
+      <c r="I38" s="151">
+        <f t="shared" si="0"/>
+        <v>1232</v>
+      </c>
+      <c r="J38" s="152"/>
+    </row>
+    <row r="39" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A39" s="148"/>
+      <c r="B39" s="153" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="154"/>
+      <c r="D39" s="107"/>
+      <c r="E39" s="90" t="str">
+        <f>VLOOKUP(B39,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F39" s="122">
+        <v>9000</v>
+      </c>
+      <c r="G39" s="155">
+        <f>VLOOKUP(B39,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.251</v>
+      </c>
+      <c r="H39" s="155"/>
+      <c r="I39" s="151">
+        <f t="shared" si="0"/>
+        <v>2259</v>
+      </c>
+      <c r="J39" s="152"/>
+    </row>
+    <row r="40" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A40" s="148"/>
+      <c r="B40" s="153" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="154"/>
+      <c r="D40" s="107"/>
+      <c r="E40" s="90" t="str">
+        <f>VLOOKUP(B40,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F40" s="122">
+        <v>5500</v>
+      </c>
+      <c r="G40" s="155">
+        <f>VLOOKUP(B40,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.224</v>
+      </c>
+      <c r="H40" s="155"/>
+      <c r="I40" s="151">
+        <f t="shared" si="0"/>
+        <v>1232</v>
+      </c>
+      <c r="J40" s="152"/>
+    </row>
+    <row r="41" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A41" s="148"/>
+      <c r="B41" s="153" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="154"/>
+      <c r="D41" s="121"/>
+      <c r="E41" s="90" t="str">
+        <f>VLOOKUP(B41,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>pcs</v>
+      </c>
+      <c r="F41" s="122">
+        <v>13500</v>
+      </c>
+      <c r="G41" s="155">
+        <f>VLOOKUP(B41,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>0.224</v>
+      </c>
+      <c r="H41" s="155"/>
+      <c r="I41" s="151">
+        <f t="shared" si="0"/>
+        <v>3024</v>
+      </c>
+      <c r="J41" s="152"/>
+    </row>
+    <row r="42" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A42" s="148"/>
+      <c r="B42" s="153"/>
+      <c r="C42" s="154"/>
+      <c r="D42" s="116"/>
+      <c r="E42" s="90" t="e">
+        <f>VLOOKUP(B42,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F42" s="122">
+        <v>13000</v>
+      </c>
+      <c r="G42" s="155" t="e">
+        <f>VLOOKUP(B42,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H42" s="155"/>
+      <c r="I42" s="151" t="str">
+        <f t="shared" ref="I42:I48" si="1">IFERROR(G42*F42, "")</f>
+        <v/>
+      </c>
+      <c r="J42" s="152"/>
+    </row>
+    <row r="43" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A43" s="148"/>
+      <c r="B43" s="153"/>
+      <c r="C43" s="154"/>
+      <c r="D43" s="116"/>
+      <c r="E43" s="90" t="e">
+        <f>VLOOKUP(B43,データ!$B$3:$DH$185,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F43" s="123">
+        <v>7</v>
+      </c>
+      <c r="G43" s="155" t="e">
+        <f>VLOOKUP(B43,データ!$B$3:$C$185,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H43" s="155"/>
+      <c r="I43" s="151" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J43" s="152"/>
+    </row>
+    <row r="44" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A44" s="148"/>
+      <c r="B44" s="153"/>
+      <c r="C44" s="154"/>
+      <c r="D44" s="116"/>
+      <c r="E44" s="90" t="e">
+        <f>VLOOKUP(B44,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F44" s="122">
+        <v>12000</v>
+      </c>
+      <c r="G44" s="155" t="e">
+        <f>VLOOKUP(B44,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H44" s="155"/>
+      <c r="I44" s="151" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J44" s="152"/>
+    </row>
+    <row r="45" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A45" s="149"/>
+      <c r="B45" s="153"/>
+      <c r="C45" s="154"/>
+      <c r="D45" s="116"/>
+      <c r="E45" s="90" t="e">
+        <f>VLOOKUP(B45,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F45" s="126">
+        <v>240</v>
+      </c>
+      <c r="G45" s="155" t="e">
+        <f>VLOOKUP(B45,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H45" s="155"/>
+      <c r="I45" s="151" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J45" s="152"/>
+    </row>
+    <row r="46" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A46" s="148"/>
+      <c r="B46" s="153"/>
+      <c r="C46" s="154"/>
+      <c r="D46" s="116"/>
+      <c r="E46" s="90" t="e">
+        <f>VLOOKUP(B46,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F46" s="122">
+        <v>13000</v>
+      </c>
+      <c r="G46" s="155" t="e">
+        <f>VLOOKUP(B46,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H46" s="155"/>
+      <c r="I46" s="151" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J46" s="152"/>
+    </row>
+    <row r="47" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A47" s="148"/>
+      <c r="B47" s="153"/>
+      <c r="C47" s="154"/>
+      <c r="D47" s="116"/>
+      <c r="E47" s="90" t="e">
+        <f>VLOOKUP(B47,データ!$B$3:$DH$185,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F47" s="123">
+        <v>7</v>
+      </c>
+      <c r="G47" s="155" t="e">
+        <f>VLOOKUP(B47,データ!$B$3:$C$185,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H47" s="155"/>
+      <c r="I47" s="151" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J47" s="152"/>
+    </row>
+    <row r="48" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A48" s="148"/>
+      <c r="B48" s="153"/>
+      <c r="C48" s="154"/>
+      <c r="D48" s="116"/>
+      <c r="E48" s="90" t="e">
+        <f>VLOOKUP(B48,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F48" s="122">
+        <v>12000</v>
+      </c>
+      <c r="G48" s="155" t="e">
+        <f>VLOOKUP(B48,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H48" s="155"/>
+      <c r="I48" s="151" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J48" s="152"/>
+    </row>
+    <row r="49" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A49" s="148"/>
+      <c r="B49" s="153"/>
+      <c r="C49" s="154"/>
+      <c r="D49" s="116"/>
+      <c r="E49" s="90" t="e">
+        <f>VLOOKUP(B49,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F49" s="122">
+        <v>13000</v>
+      </c>
+      <c r="G49" s="155" t="e">
+        <f>VLOOKUP(B49,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H49" s="155"/>
+      <c r="I49" s="151" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J49" s="152"/>
+    </row>
+    <row r="50" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A50" s="148"/>
+      <c r="B50" s="153"/>
+      <c r="C50" s="154"/>
+      <c r="D50" s="116"/>
+      <c r="E50" s="90" t="e">
+        <f>VLOOKUP(B50,データ!$B$3:$DH$185,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F50" s="123">
+        <v>7</v>
+      </c>
+      <c r="G50" s="155" t="e">
+        <f>VLOOKUP(B50,データ!$B$3:$C$185,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H50" s="155"/>
+      <c r="I50" s="151" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J50" s="152"/>
+    </row>
+    <row r="51" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A51" s="148"/>
+      <c r="B51" s="153"/>
+      <c r="C51" s="154"/>
+      <c r="D51" s="116"/>
+      <c r="E51" s="90" t="e">
+        <f>VLOOKUP(B51,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F51" s="122">
+        <v>12000</v>
+      </c>
+      <c r="G51" s="155" t="e">
+        <f>VLOOKUP(B51,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H51" s="155"/>
+      <c r="I51" s="151" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J51" s="152"/>
+    </row>
+    <row r="52" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A52" s="149"/>
+      <c r="B52" s="153"/>
+      <c r="C52" s="154"/>
+      <c r="D52" s="116"/>
+      <c r="E52" s="90" t="e">
+        <f>VLOOKUP(B52,データ!$B$3:$L$85,11,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F52" s="126">
+        <v>240</v>
+      </c>
+      <c r="G52" s="155" t="e">
+        <f>VLOOKUP(B52,データ!$B$3:$C$85,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H52" s="155"/>
+      <c r="I52" s="151" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J52" s="152"/>
+    </row>
+    <row r="53" spans="1:10" ht="19.7" customHeight="1">
+      <c r="A53" s="160" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="161"/>
+      <c r="C53" s="161"/>
+      <c r="D53" s="161"/>
+      <c r="E53" s="161"/>
+      <c r="F53" s="164"/>
+      <c r="G53" s="165"/>
+      <c r="H53" s="166"/>
+      <c r="I53" s="156">
+        <f>SUM(I33:K52)</f>
+        <v>17618</v>
+      </c>
+      <c r="J53" s="157"/>
+    </row>
+    <row r="54" spans="1:10" ht="24.75" customHeight="1" thickBot="1">
+      <c r="A54" s="162"/>
+      <c r="B54" s="163"/>
+      <c r="C54" s="163"/>
+      <c r="D54" s="163"/>
+      <c r="E54" s="163"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="168"/>
+      <c r="H54" s="169"/>
+      <c r="I54" s="158"/>
+      <c r="J54" s="159"/>
+    </row>
+    <row r="55" spans="1:10" ht="11.25" customHeight="1"/>
+    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1">
+      <c r="A56" s="174" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" s="174"/>
+      <c r="C56" s="174"/>
+      <c r="D56" s="98"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="173" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56" s="173"/>
+      <c r="I56" s="173"/>
+      <c r="J56" s="64"/>
+    </row>
+    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1">
+      <c r="A57" s="172" t="s">
+        <v>119</v>
+      </c>
+      <c r="B57" s="172"/>
+      <c r="C57" s="172"/>
+      <c r="D57" s="99"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="9"/>
+    </row>
+    <row r="58" spans="1:10" ht="20.100000000000001" customHeight="1">
+      <c r="A58" s="171"/>
+      <c r="B58" s="171"/>
+      <c r="C58" s="171"/>
+      <c r="D58" s="91"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="34"/>
+    </row>
+    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1">
+      <c r="A59" s="175"/>
+      <c r="B59" s="175"/>
+      <c r="C59" s="175"/>
+      <c r="D59" s="97"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34"/>
+    </row>
+    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1">
+      <c r="A60" s="171"/>
+      <c r="B60" s="171"/>
+      <c r="C60" s="171"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells count="95">
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A1:K4"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="G8:J10"/>
+    <mergeCell ref="G11:H12"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J19"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="A26:E28"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:H32"/>
+    <mergeCell ref="I30:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="A53:E54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="F53:H54"/>
+    <mergeCell ref="I53:J54"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.22" right="0" top="0.16" bottom="0" header="0.16" footer="0"/>
+  <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{58860D42-9B30-465F-98D0-64908A640804}">
+          <x14:formula1>
+            <xm:f>データ!$B$3:$B$112</xm:f>
+          </x14:formula1>
+          <xm:sqref>B50:C50 B43:C43 B47:C47</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5C33DA74-8EBD-4A79-8750-7652C2991AF3}">
+          <x14:formula1>
+            <xm:f>データ!$B$3:$B$85</xm:f>
+          </x14:formula1>
+          <xm:sqref>B33:B34 B36:B37 B35:C35 B51:C52 B38:C42 B44:C46 B48:C49</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE01DD97-DBB0-4157-9B8B-78D146674406}">
+  <dimension ref="A1:R103"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9" style="21"/>
+    <col min="3" max="3" width="33.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="10.375" style="21" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="7.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="10" style="21" customWidth="1"/>
+    <col min="11" max="11" width="11.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.875" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="21"/>
+    <col min="18" max="18" width="10" style="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" customHeight="1">
+      <c r="A1" s="255" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="255"/>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
+      <c r="F1" s="255"/>
+      <c r="G1" s="255"/>
+      <c r="H1" s="255"/>
+      <c r="I1" s="255"/>
+      <c r="J1" s="255"/>
+      <c r="K1" s="255"/>
+    </row>
+    <row r="2" spans="1:11" ht="7.5" customHeight="1">
+      <c r="A2" s="255"/>
+      <c r="B2" s="255"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+    </row>
+    <row r="3" spans="1:11" ht="9.75" customHeight="1">
+      <c r="A3" s="255"/>
+      <c r="B3" s="255"/>
+      <c r="C3" s="255"/>
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="255"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="255"/>
+      <c r="K3" s="255"/>
+    </row>
+    <row r="4" spans="1:11" ht="12.75" hidden="1" customHeight="1">
+      <c r="A4" s="255"/>
+      <c r="B4" s="255"/>
+      <c r="C4" s="255"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="H5" s="277" t="str">
+        <f>INVOICE!G5</f>
+        <v>インボイス作成日（Date): 5/12/2025</v>
+      </c>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="277"/>
+    </row>
+    <row r="7" spans="1:11" ht="9.75" customHeight="1" thickBot="1"/>
+    <row r="8" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A8" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="184" t="str">
+        <f>INVOICE!G8</f>
+        <v>Invoice No
+MASUDA VN-JP 019/25</v>
+      </c>
+      <c r="I8" s="185"/>
+      <c r="J8" s="185"/>
+      <c r="K8" s="186"/>
+    </row>
+    <row r="9" spans="1:11" ht="9.75" customHeight="1">
+      <c r="A9" s="25"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="188"/>
+      <c r="J9" s="188"/>
+      <c r="K9" s="189"/>
+    </row>
+    <row r="10" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A10" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="188"/>
+      <c r="J10" s="188"/>
+      <c r="K10" s="189"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1">
+      <c r="A11" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="246" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="246"/>
+      <c r="J11" s="244" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="245"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="73" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="246"/>
+      <c r="I12" s="246"/>
+      <c r="J12" s="244"/>
+      <c r="K12" s="245"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="247" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="247"/>
+      <c r="J13" s="247" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="248"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="249" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
+      <c r="K14" s="250"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1">
+      <c r="A15" s="73"/>
+      <c r="B15" s="1"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="257" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="258"/>
+      <c r="J15" s="258"/>
+      <c r="K15" s="259"/>
+    </row>
+    <row r="16" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
+      <c r="K16" s="259"/>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="261"/>
+      <c r="J17" s="261"/>
+      <c r="K17" s="262"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" hidden="1" customHeight="1">
+      <c r="A18" s="30"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="31"/>
+    </row>
+    <row r="19" spans="1:18" ht="6" customHeight="1">
+      <c r="A19" s="30"/>
+      <c r="G19" s="43"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="31"/>
+    </row>
+    <row r="20" spans="1:18" ht="18.75">
+      <c r="A20" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="31"/>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="G21" s="43"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="215" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="216"/>
+      <c r="C23" s="216"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="81"/>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="31"/>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="265" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="266"/>
+      <c r="C24" s="266"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="43"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="K24" s="31"/>
+    </row>
+    <row r="25" spans="1:18" ht="12.75" customHeight="1">
+      <c r="A25" s="35"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="226"/>
+      <c r="D25" s="226"/>
+      <c r="E25" s="226"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="81"/>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="31"/>
+    </row>
+    <row r="26" spans="1:18" ht="18.75">
+      <c r="A26" s="229" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="230"/>
+      <c r="C26" s="230"/>
+      <c r="D26" s="230"/>
+      <c r="E26" s="230"/>
+      <c r="F26" s="278"/>
+      <c r="G26" s="272" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" s="81"/>
+      <c r="I26" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="31"/>
+    </row>
+    <row r="27" spans="1:18" ht="12.75" customHeight="1">
+      <c r="A27" s="231"/>
+      <c r="B27" s="232"/>
+      <c r="C27" s="232"/>
+      <c r="D27" s="232"/>
+      <c r="E27" s="232"/>
+      <c r="F27" s="269"/>
+      <c r="G27" s="273"/>
+      <c r="H27" s="81"/>
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="31"/>
+    </row>
+    <row r="28" spans="1:18" ht="11.25" customHeight="1">
+      <c r="A28" s="233"/>
+      <c r="B28" s="234"/>
+      <c r="C28" s="234"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="234"/>
+      <c r="F28" s="270"/>
+      <c r="G28" s="273"/>
+      <c r="K28" s="31"/>
+    </row>
+    <row r="29" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A29" s="235"/>
+      <c r="B29" s="236"/>
+      <c r="C29" s="236"/>
+      <c r="D29" s="236"/>
+      <c r="E29" s="236"/>
+      <c r="F29" s="271"/>
+      <c r="G29" s="274"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="32"/>
+    </row>
+    <row r="30" spans="1:18" ht="9.75" customHeight="1" thickBot="1">
+      <c r="A30" s="91"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="92"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" customHeight="1">
+      <c r="A31" s="217" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="180" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="181"/>
+      <c r="D31" s="238" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="170" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="220" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="180" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="181"/>
+      <c r="I31" s="263" t="s">
+        <v>45</v>
+      </c>
+      <c r="J31" s="238" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" s="251" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="11.25" customHeight="1">
+      <c r="A32" s="267"/>
+      <c r="B32" s="182"/>
+      <c r="C32" s="183"/>
+      <c r="D32" s="239"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="222"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="183"/>
+      <c r="I32" s="264"/>
+      <c r="J32" s="254"/>
+      <c r="K32" s="252"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="56"/>
+      <c r="R32" s="56"/>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="267"/>
+      <c r="B33" s="182"/>
+      <c r="C33" s="183"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="222"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="183"/>
+      <c r="I33" s="264"/>
+      <c r="J33" s="254"/>
+      <c r="K33" s="252"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="59"/>
+      <c r="P33" s="60"/>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="60"/>
+    </row>
+    <row r="34" spans="1:18" ht="10.5" customHeight="1">
+      <c r="A34" s="268"/>
+      <c r="B34" s="182"/>
+      <c r="C34" s="183"/>
+      <c r="D34" s="276"/>
+      <c r="E34" s="256"/>
+      <c r="F34" s="275"/>
+      <c r="G34" s="182"/>
+      <c r="H34" s="183"/>
+      <c r="I34" s="264"/>
+      <c r="J34" s="254"/>
+      <c r="K34" s="253"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="132"/>
+      <c r="N34" s="101"/>
+      <c r="O34" s="133"/>
+      <c r="P34" s="134"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+    </row>
+    <row r="35" spans="1:18" ht="21" customHeight="1">
+      <c r="A35" s="148" t="str">
+        <f>IF('INVOICE-20'!A33 &lt;&gt; "", 'INVOICE-20'!A33, "")</f>
+        <v/>
+      </c>
+      <c r="B35" s="240" t="str">
+        <f>'INVOICE-20'!B33</f>
+        <v>TABLE EDGE MG23</v>
+      </c>
+      <c r="C35" s="241"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="108" t="str">
+        <f>'INVOICE-20'!E33</f>
+        <v>m</v>
+      </c>
+      <c r="F35" s="111">
+        <f>'INVOICE-20'!F33</f>
+        <v>4000</v>
+      </c>
+      <c r="G35" s="242"/>
+      <c r="H35" s="243"/>
+      <c r="I35" s="124" t="str">
+        <f>IFERROR(ROUNDUP(F35/G35,0), "")</f>
+        <v/>
+      </c>
+      <c r="J35" s="131"/>
+      <c r="K35" s="113">
+        <f>ROUND(N35+P35+20,2)</f>
+        <v>20</v>
+      </c>
+      <c r="L35" s="56"/>
+      <c r="M35" s="132"/>
+      <c r="N35" s="135"/>
+      <c r="O35" s="134"/>
+      <c r="P35" s="132"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+    </row>
+    <row r="36" spans="1:18" ht="21" customHeight="1">
+      <c r="A36" s="148" t="str">
+        <f>IF('INVOICE-20'!A34 &lt;&gt; "", 'INVOICE-20'!A34, "")</f>
+        <v/>
+      </c>
+      <c r="B36" s="240" t="str">
+        <f>'INVOICE-20'!B34</f>
+        <v>PUROTEKUTA 55788-16110</v>
+      </c>
+      <c r="C36" s="241"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108" t="str">
+        <f>'INVOICE-20'!E34</f>
+        <v>pcs</v>
+      </c>
+      <c r="F36" s="111">
+        <f>'INVOICE-20'!F34</f>
+        <v>11000</v>
+      </c>
+      <c r="G36" s="242"/>
+      <c r="H36" s="243"/>
+      <c r="I36" s="124" t="str">
+        <f t="shared" ref="I36:I54" si="0">IFERROR(ROUNDUP(F36/G36,0), "")</f>
+        <v/>
+      </c>
+      <c r="J36" s="131"/>
+      <c r="K36" s="113">
+        <f>ROUND(N36+P36,2)+10</f>
+        <v>10</v>
+      </c>
+      <c r="L36" s="56"/>
+      <c r="M36" s="132"/>
+      <c r="N36" s="135"/>
+      <c r="O36" s="134"/>
+      <c r="P36" s="132"/>
+      <c r="Q36" s="60"/>
+      <c r="R36" s="60"/>
+    </row>
+    <row r="37" spans="1:18" ht="21" customHeight="1">
+      <c r="A37" s="148" t="str">
+        <f>IF('INVOICE-20'!A35 &lt;&gt; "", 'INVOICE-20'!A35, "")</f>
+        <v/>
+      </c>
+      <c r="B37" s="240" t="str">
+        <f>'INVOICE-20'!B35</f>
+        <v>PUROTEKUTA 55788-52350</v>
+      </c>
+      <c r="C37" s="241"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="108" t="str">
+        <f>'INVOICE-20'!E35</f>
+        <v>pcs</v>
+      </c>
+      <c r="F37" s="111">
+        <f>'INVOICE-20'!F35</f>
+        <v>6000</v>
+      </c>
+      <c r="G37" s="242"/>
+      <c r="H37" s="243"/>
+      <c r="I37" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J37" s="131"/>
+      <c r="K37" s="113">
+        <f>ROUND(N37+P37,2)+5</f>
+        <v>5</v>
+      </c>
+      <c r="L37" s="56"/>
+      <c r="M37" s="132"/>
+      <c r="N37" s="135"/>
+      <c r="O37" s="134"/>
+      <c r="P37" s="132"/>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="60"/>
+    </row>
+    <row r="38" spans="1:18" ht="21" customHeight="1">
+      <c r="A38" s="148" t="str">
+        <f>IF('INVOICE-20'!A36 &lt;&gt; "", 'INVOICE-20'!A36, "")</f>
+        <v/>
+      </c>
+      <c r="B38" s="240" t="str">
+        <f>'INVOICE-20'!B36</f>
+        <v>PUROTEKUTA 55788-52360</v>
+      </c>
+      <c r="C38" s="241"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108" t="str">
+        <f>'INVOICE-20'!E36</f>
+        <v>pcs</v>
+      </c>
+      <c r="F38" s="111">
+        <f>'INVOICE-20'!F36</f>
+        <v>5000</v>
+      </c>
+      <c r="G38" s="242"/>
+      <c r="H38" s="243"/>
+      <c r="I38" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J38" s="131"/>
+      <c r="K38" s="113">
+        <f>ROUND(N38+P38,2)+5</f>
+        <v>5</v>
+      </c>
+      <c r="L38" s="56"/>
+      <c r="M38" s="132"/>
+      <c r="N38" s="135"/>
+      <c r="O38" s="134"/>
+      <c r="P38" s="132"/>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+    </row>
+    <row r="39" spans="1:18" ht="21" customHeight="1">
+      <c r="A39" s="148" t="str">
+        <f>IF('INVOICE-20'!A37 &lt;&gt; "", 'INVOICE-20'!A37, "")</f>
+        <v/>
+      </c>
+      <c r="B39" s="240" t="str">
+        <f>'INVOICE-20'!B37</f>
+        <v>PUROTEKUTA 2A4P1-022G</v>
+      </c>
+      <c r="C39" s="241"/>
+      <c r="D39" s="121"/>
+      <c r="E39" s="108" t="str">
+        <f>'INVOICE-20'!E37</f>
+        <v>pcs</v>
+      </c>
+      <c r="F39" s="111">
+        <f>'INVOICE-20'!F37</f>
+        <v>11000</v>
+      </c>
+      <c r="G39" s="242"/>
+      <c r="H39" s="243"/>
+      <c r="I39" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J39" s="131"/>
+      <c r="K39" s="113">
+        <f>ROUND(N39+P39,2)+10</f>
+        <v>10</v>
+      </c>
+      <c r="L39" s="56"/>
+      <c r="M39" s="132"/>
+      <c r="N39" s="135"/>
+      <c r="O39" s="134"/>
+      <c r="P39" s="132"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+    </row>
+    <row r="40" spans="1:18" ht="21" customHeight="1">
+      <c r="A40" s="148" t="str">
+        <f>IF('INVOICE-20'!A38 &lt;&gt; "", 'INVOICE-20'!A38, "")</f>
+        <v/>
+      </c>
+      <c r="B40" s="240" t="str">
+        <f>'INVOICE-20'!B38</f>
+        <v>PUROTEKUTA 55788-K0060</v>
+      </c>
+      <c r="C40" s="241"/>
+      <c r="E40" s="108" t="str">
+        <f>'INVOICE-20'!E38</f>
+        <v>pcs</v>
+      </c>
+      <c r="F40" s="111">
+        <f>'INVOICE-20'!F38</f>
+        <v>5500</v>
+      </c>
+      <c r="G40" s="242"/>
+      <c r="H40" s="243"/>
+      <c r="I40" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J40" s="131"/>
+      <c r="K40" s="113">
+        <f t="shared" ref="K40:K54" si="1">ROUND(N40+P40,2)+10</f>
+        <v>10</v>
+      </c>
+      <c r="L40" s="56"/>
+      <c r="M40" s="132"/>
+      <c r="N40" s="135"/>
+      <c r="O40" s="134"/>
+      <c r="P40" s="132"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+    </row>
+    <row r="41" spans="1:18" ht="21" customHeight="1">
+      <c r="A41" s="148" t="str">
+        <f>IF('INVOICE-20'!A39 &lt;&gt; "", 'INVOICE-20'!A39, "")</f>
+        <v/>
+      </c>
+      <c r="B41" s="240" t="str">
+        <f>'INVOICE-20'!B39</f>
+        <v>PUROTEKUTA 55788-48090</v>
+      </c>
+      <c r="C41" s="241"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="108" t="str">
+        <f>'INVOICE-20'!E39</f>
+        <v>pcs</v>
+      </c>
+      <c r="F41" s="111">
+        <f>'INVOICE-20'!F39</f>
+        <v>9000</v>
+      </c>
+      <c r="G41" s="242"/>
+      <c r="H41" s="243"/>
+      <c r="I41" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J41" s="131"/>
+      <c r="K41" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L41" s="56"/>
+      <c r="M41" s="132"/>
+      <c r="N41" s="135"/>
+      <c r="O41" s="134"/>
+      <c r="P41" s="132"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+    </row>
+    <row r="42" spans="1:18" ht="21" customHeight="1">
+      <c r="A42" s="148" t="str">
+        <f>IF('INVOICE-20'!A40 &lt;&gt; "", 'INVOICE-20'!A40, "")</f>
+        <v/>
+      </c>
+      <c r="B42" s="240" t="str">
+        <f>'INVOICE-20'!B40</f>
+        <v>PUROTEKUTA 55788-K0060</v>
+      </c>
+      <c r="C42" s="241"/>
+      <c r="D42" s="108"/>
+      <c r="E42" s="108" t="str">
+        <f>'INVOICE-20'!E40</f>
+        <v>pcs</v>
+      </c>
+      <c r="F42" s="111">
+        <f>'INVOICE-20'!F40</f>
+        <v>5500</v>
+      </c>
+      <c r="G42" s="242"/>
+      <c r="H42" s="243"/>
+      <c r="I42" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J42" s="131"/>
+      <c r="K42" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L42" s="132"/>
+      <c r="M42" s="132"/>
+      <c r="N42" s="135"/>
+      <c r="O42" s="134"/>
+      <c r="P42" s="132"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="60"/>
+    </row>
+    <row r="43" spans="1:18" ht="21" customHeight="1">
+      <c r="A43" s="148" t="str">
+        <f>IF('INVOICE-20'!A41 &lt;&gt; "", 'INVOICE-20'!A41, "")</f>
+        <v/>
+      </c>
+      <c r="B43" s="240" t="str">
+        <f>'INVOICE-20'!B41</f>
+        <v>PUROTEKUTA 55788-K0060</v>
+      </c>
+      <c r="C43" s="241"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108" t="str">
+        <f>'INVOICE-20'!E41</f>
+        <v>pcs</v>
+      </c>
+      <c r="F43" s="111">
+        <f>'INVOICE-20'!F41</f>
+        <v>13500</v>
+      </c>
+      <c r="G43" s="242"/>
+      <c r="H43" s="243"/>
+      <c r="I43" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J43" s="131"/>
+      <c r="K43" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L43" s="132"/>
+      <c r="M43" s="132"/>
+      <c r="N43" s="135"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="132"/>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="60"/>
+    </row>
+    <row r="44" spans="1:18" ht="21" customHeight="1">
+      <c r="A44" s="148" t="str">
+        <f>IF('INVOICE-20'!A42 &lt;&gt; "", 'INVOICE-20'!A42, "")</f>
+        <v/>
+      </c>
+      <c r="B44" s="240">
+        <f>'INVOICE-20'!B42</f>
+        <v>0</v>
+      </c>
+      <c r="C44" s="241"/>
+      <c r="D44" s="108"/>
+      <c r="E44" s="108" t="e">
+        <f>'INVOICE-20'!E42</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F44" s="111">
+        <f>'INVOICE-20'!F42</f>
+        <v>13000</v>
+      </c>
+      <c r="G44" s="242"/>
+      <c r="H44" s="243"/>
+      <c r="I44" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J44" s="131"/>
+      <c r="K44" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L44" s="132"/>
+      <c r="M44" s="132"/>
+      <c r="N44" s="135"/>
+      <c r="O44" s="134"/>
+      <c r="P44" s="132"/>
+      <c r="Q44" s="60"/>
+      <c r="R44" s="60"/>
+    </row>
+    <row r="45" spans="1:18" ht="21" customHeight="1">
+      <c r="A45" s="148" t="str">
+        <f>IF('INVOICE-20'!A43 &lt;&gt; "", 'INVOICE-20'!A43, "")</f>
+        <v/>
+      </c>
+      <c r="B45" s="240">
+        <f>'INVOICE-20'!B43</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="241"/>
+      <c r="D45" s="108"/>
+      <c r="E45" s="108" t="e">
+        <f>'INVOICE-20'!E43</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F45" s="111">
+        <f>'INVOICE-20'!F43</f>
+        <v>7</v>
+      </c>
+      <c r="G45" s="242"/>
+      <c r="H45" s="243"/>
+      <c r="I45" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J45" s="131"/>
+      <c r="K45" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L45" s="56"/>
+      <c r="M45" s="132"/>
+      <c r="N45" s="135"/>
+      <c r="O45" s="134"/>
+      <c r="P45" s="132"/>
+      <c r="Q45" s="60"/>
+      <c r="R45" s="60"/>
+    </row>
+    <row r="46" spans="1:18" ht="21" customHeight="1">
+      <c r="A46" s="148" t="str">
+        <f>IF('INVOICE-20'!A44 &lt;&gt; "", 'INVOICE-20'!A44, "")</f>
+        <v/>
+      </c>
+      <c r="B46" s="240">
+        <f>'INVOICE-20'!B44</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="241"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108" t="e">
+        <f>'INVOICE-20'!E44</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F46" s="111">
+        <f>'INVOICE-20'!F44</f>
+        <v>12000</v>
+      </c>
+      <c r="G46" s="242"/>
+      <c r="H46" s="243"/>
+      <c r="I46" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J46" s="131"/>
+      <c r="K46" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L46" s="56"/>
+      <c r="M46" s="132"/>
+      <c r="N46" s="135"/>
+      <c r="O46" s="134"/>
+      <c r="P46" s="132"/>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="60"/>
+    </row>
+    <row r="47" spans="1:18" ht="21" customHeight="1">
+      <c r="A47" s="148" t="str">
+        <f>IF('INVOICE-20'!A45 &lt;&gt; "", 'INVOICE-20'!A45, "")</f>
+        <v/>
+      </c>
+      <c r="B47" s="240">
+        <f>'INVOICE-20'!B45</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="241"/>
+      <c r="E47" s="108" t="e">
+        <f>'INVOICE-20'!E45</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F47" s="111">
+        <f>'INVOICE-20'!F45</f>
+        <v>240</v>
+      </c>
+      <c r="G47" s="242"/>
+      <c r="H47" s="243"/>
+      <c r="I47" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J47" s="131"/>
+      <c r="K47" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L47" s="56"/>
+      <c r="M47" s="132"/>
+      <c r="N47" s="135"/>
+      <c r="O47" s="134"/>
+      <c r="P47" s="132"/>
+      <c r="Q47" s="60"/>
+      <c r="R47" s="60"/>
+    </row>
+    <row r="48" spans="1:18" ht="21" customHeight="1">
+      <c r="A48" s="148" t="str">
+        <f>IF('INVOICE-20'!A46 &lt;&gt; "", 'INVOICE-20'!A46, "")</f>
+        <v/>
+      </c>
+      <c r="B48" s="240">
+        <f>'INVOICE-20'!B46</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="241"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="108" t="e">
+        <f>'INVOICE-20'!E46</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F48" s="111">
+        <f>'INVOICE-20'!F46</f>
+        <v>13000</v>
+      </c>
+      <c r="G48" s="242"/>
+      <c r="H48" s="243"/>
+      <c r="I48" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J48" s="131"/>
+      <c r="K48" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L48" s="56"/>
+      <c r="M48" s="132"/>
+      <c r="N48" s="135"/>
+      <c r="O48" s="134"/>
+      <c r="P48" s="132"/>
+      <c r="Q48" s="60"/>
+      <c r="R48" s="60"/>
+    </row>
+    <row r="49" spans="1:18" ht="21" customHeight="1">
+      <c r="A49" s="148" t="str">
+        <f>IF('INVOICE-20'!A47 &lt;&gt; "", 'INVOICE-20'!A47, "")</f>
+        <v/>
+      </c>
+      <c r="B49" s="240">
+        <f>'INVOICE-20'!B47</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="241"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108" t="e">
+        <f>'INVOICE-20'!E47</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F49" s="111">
+        <f>'INVOICE-20'!F47</f>
+        <v>7</v>
+      </c>
+      <c r="G49" s="242"/>
+      <c r="H49" s="243"/>
+      <c r="I49" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J49" s="131"/>
+      <c r="K49" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L49" s="132"/>
+      <c r="M49" s="132"/>
+      <c r="N49" s="135"/>
+      <c r="O49" s="134"/>
+      <c r="P49" s="132"/>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="60"/>
+    </row>
+    <row r="50" spans="1:18" ht="21" customHeight="1">
+      <c r="A50" s="148" t="str">
+        <f>IF('INVOICE-20'!A48 &lt;&gt; "", 'INVOICE-20'!A48, "")</f>
+        <v/>
+      </c>
+      <c r="B50" s="240">
+        <f>'INVOICE-20'!B48</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="241"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="108" t="e">
+        <f>'INVOICE-20'!E48</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F50" s="111">
+        <f>'INVOICE-20'!F48</f>
+        <v>12000</v>
+      </c>
+      <c r="G50" s="242"/>
+      <c r="H50" s="243"/>
+      <c r="I50" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J50" s="131"/>
+      <c r="K50" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L50" s="132"/>
+      <c r="M50" s="132"/>
+      <c r="N50" s="135"/>
+      <c r="O50" s="134"/>
+      <c r="P50" s="132"/>
+      <c r="Q50" s="60"/>
+      <c r="R50" s="60"/>
+    </row>
+    <row r="51" spans="1:18" ht="21" customHeight="1">
+      <c r="A51" s="148" t="str">
+        <f>IF('INVOICE-20'!A49 &lt;&gt; "", 'INVOICE-20'!A49, "")</f>
+        <v/>
+      </c>
+      <c r="B51" s="240">
+        <f>'INVOICE-20'!B49</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="241"/>
+      <c r="D51" s="108"/>
+      <c r="E51" s="108" t="e">
+        <f>'INVOICE-20'!E49</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F51" s="111">
+        <f>'INVOICE-20'!F49</f>
+        <v>13000</v>
+      </c>
+      <c r="G51" s="242"/>
+      <c r="H51" s="243"/>
+      <c r="I51" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J51" s="131"/>
+      <c r="K51" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L51" s="132"/>
+      <c r="M51" s="132"/>
+      <c r="N51" s="135"/>
+      <c r="O51" s="134"/>
+      <c r="P51" s="132"/>
+      <c r="Q51" s="60"/>
+      <c r="R51" s="60"/>
+    </row>
+    <row r="52" spans="1:18" ht="21" customHeight="1">
+      <c r="A52" s="148" t="str">
+        <f>IF('INVOICE-20'!A50 &lt;&gt; "", 'INVOICE-20'!A50, "")</f>
+        <v/>
+      </c>
+      <c r="B52" s="240">
+        <f>'INVOICE-20'!B50</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="241"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="108" t="e">
+        <f>'INVOICE-20'!E50</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F52" s="111">
+        <f>'INVOICE-20'!F50</f>
+        <v>7</v>
+      </c>
+      <c r="G52" s="242"/>
+      <c r="H52" s="243"/>
+      <c r="I52" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J52" s="131"/>
+      <c r="K52" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L52" s="56"/>
+      <c r="M52" s="132"/>
+      <c r="N52" s="135"/>
+      <c r="O52" s="134"/>
+      <c r="P52" s="132"/>
+      <c r="Q52" s="60"/>
+      <c r="R52" s="60"/>
+    </row>
+    <row r="53" spans="1:18" ht="21" customHeight="1">
+      <c r="A53" s="148" t="str">
+        <f>IF('INVOICE-20'!A51 &lt;&gt; "", 'INVOICE-20'!A51, "")</f>
+        <v/>
+      </c>
+      <c r="B53" s="240">
+        <f>'INVOICE-20'!B51</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="241"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="108" t="e">
+        <f>'INVOICE-20'!E51</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F53" s="111">
+        <f>'INVOICE-20'!F51</f>
+        <v>12000</v>
+      </c>
+      <c r="G53" s="242"/>
+      <c r="H53" s="243"/>
+      <c r="I53" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J53" s="131"/>
+      <c r="K53" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L53" s="56"/>
+      <c r="M53" s="132"/>
+      <c r="N53" s="135"/>
+      <c r="O53" s="134"/>
+      <c r="P53" s="132"/>
+      <c r="Q53" s="60"/>
+      <c r="R53" s="60"/>
+    </row>
+    <row r="54" spans="1:18" ht="21" customHeight="1">
+      <c r="A54" s="148" t="str">
+        <f>IF('INVOICE-20'!A52 &lt;&gt; "", 'INVOICE-20'!A52, "")</f>
+        <v/>
+      </c>
+      <c r="B54" s="240">
+        <f>'INVOICE-20'!B52</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="241"/>
+      <c r="D54" s="125"/>
+      <c r="E54" s="108" t="e">
+        <f>'INVOICE-20'!E52</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F54" s="111">
+        <f>'INVOICE-20'!F52</f>
+        <v>240</v>
+      </c>
+      <c r="G54" s="242"/>
+      <c r="H54" s="243"/>
+      <c r="I54" s="124" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J54" s="119"/>
+      <c r="K54" s="113">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="M54" s="132"/>
+      <c r="N54" s="135"/>
+      <c r="O54" s="134"/>
+      <c r="P54" s="132"/>
+      <c r="Q54" s="60"/>
+      <c r="R54" s="60"/>
+    </row>
+    <row r="55" spans="1:18" ht="17.25" customHeight="1">
+      <c r="A55" s="280" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="203"/>
+      <c r="C55" s="203"/>
+      <c r="D55" s="203"/>
+      <c r="E55" s="204"/>
+      <c r="F55" s="285">
+        <f>SUMIF(E35:E54,L42,F35:F54)</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="287"/>
+      <c r="H55" s="204"/>
+      <c r="I55" s="295">
+        <f>SUMIF(E35:E54,L42,I35:I54)+SUMIF(E35:E54,L44,I35:I54)</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="290">
+        <f>SUM(J35:J54)</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="292">
+        <f>SUM(K35:K54)</f>
+        <v>200</v>
+      </c>
+      <c r="M55" s="132"/>
+      <c r="N55" s="135"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+    </row>
+    <row r="56" spans="1:18" ht="3.75" customHeight="1">
+      <c r="A56" s="281"/>
+      <c r="B56" s="203"/>
+      <c r="C56" s="203"/>
+      <c r="D56" s="203"/>
+      <c r="E56" s="204"/>
+      <c r="F56" s="286"/>
+      <c r="G56" s="287"/>
+      <c r="H56" s="204"/>
+      <c r="I56" s="296"/>
+      <c r="J56" s="290"/>
+      <c r="K56" s="292"/>
+      <c r="M56" s="132"/>
+      <c r="N56" s="101"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+    </row>
+    <row r="57" spans="1:18" ht="18" customHeight="1">
+      <c r="A57" s="281"/>
+      <c r="B57" s="203"/>
+      <c r="C57" s="203"/>
+      <c r="D57" s="203"/>
+      <c r="E57" s="204"/>
+      <c r="F57" s="129">
+        <f>SUMIF(E35:E54,L43,F35:F54)</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="287"/>
+      <c r="H57" s="204"/>
+      <c r="I57" s="297">
+        <f>SUMIF(E35:E54,L43,I35:I54)</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="290"/>
+      <c r="K57" s="292"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="101"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+    </row>
+    <row r="58" spans="1:18" ht="21" customHeight="1" thickBot="1">
+      <c r="A58" s="282"/>
+      <c r="B58" s="283"/>
+      <c r="C58" s="283"/>
+      <c r="D58" s="283"/>
+      <c r="E58" s="284"/>
+      <c r="F58" s="130">
+        <f>SUMIF(E35:E54,L44,F35:F54)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="288"/>
+      <c r="H58" s="284"/>
+      <c r="I58" s="298"/>
+      <c r="J58" s="291"/>
+      <c r="K58" s="293"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="101"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+    </row>
+    <row r="59" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A59" s="20" t="str">
+        <f>'INVOICE-20'!A57</f>
+        <v>CIF TO NAGOYA PORT</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="F59" s="94"/>
+      <c r="I59" s="289"/>
+      <c r="J59" s="203"/>
+      <c r="M59" s="84"/>
+      <c r="N59" s="57"/>
+    </row>
+    <row r="60" spans="1:18" ht="18" customHeight="1">
+      <c r="A60" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60" s="104">
+        <f>F55</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="86">
+        <f>F57</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="94">
+        <f>F58</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="173" t="s">
+        <v>35</v>
+      </c>
+      <c r="J60" s="173"/>
+      <c r="K60" s="173"/>
+      <c r="M60" s="95"/>
+      <c r="N60" s="57"/>
+    </row>
+    <row r="61" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A61" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" s="46">
+        <f>K55</f>
+        <v>200</v>
+      </c>
+      <c r="E61" s="110">
+        <f>J55</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="33"/>
+      <c r="H61" s="33"/>
+      <c r="I61" s="103"/>
+      <c r="J61" s="55"/>
+      <c r="K61" s="95"/>
+      <c r="N61" s="92"/>
+    </row>
+    <row r="62" spans="1:18" ht="25.5" customHeight="1">
+      <c r="A62" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" s="61">
+        <f>1.1*1.5*1.1*6+1.1*1.1*1.4+1.1*1.2*1.8*5+1.1*1.1*1</f>
+        <v>25.674000000000007</v>
+      </c>
+      <c r="F62" s="84"/>
+      <c r="N62" s="57"/>
+    </row>
+    <row r="63" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A63" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="92"/>
+      <c r="N63" s="57"/>
+    </row>
+    <row r="64" spans="1:18" ht="80.25" customHeight="1">
+      <c r="A64" s="279"/>
+      <c r="B64" s="279"/>
+      <c r="C64" s="279"/>
+      <c r="D64" s="100"/>
+    </row>
+    <row r="77" spans="5:12">
+      <c r="E77" s="136"/>
+      <c r="F77" s="136"/>
+      <c r="G77" s="136"/>
+      <c r="H77" s="136"/>
+      <c r="I77" s="136"/>
+      <c r="J77" s="136"/>
+      <c r="K77" s="136"/>
+    </row>
+    <row r="78" spans="5:12">
+      <c r="E78" s="136"/>
+      <c r="F78" s="137"/>
+      <c r="G78" s="138"/>
+      <c r="H78" s="139"/>
+      <c r="I78" s="140"/>
+      <c r="J78" s="140"/>
+      <c r="K78" s="140"/>
+    </row>
+    <row r="79" spans="5:12">
+      <c r="E79" s="136"/>
+      <c r="F79" s="137"/>
+      <c r="G79" s="138"/>
+      <c r="H79" s="139"/>
+      <c r="I79" s="140"/>
+      <c r="J79" s="140"/>
+      <c r="K79" s="140"/>
+      <c r="L79" s="52"/>
+    </row>
+    <row r="80" spans="5:12">
+      <c r="E80" s="136"/>
+      <c r="F80" s="137"/>
+      <c r="G80" s="138"/>
+      <c r="H80" s="139"/>
+      <c r="I80" s="140"/>
+      <c r="J80" s="140"/>
+      <c r="K80" s="140"/>
+      <c r="L80" s="52"/>
+    </row>
+    <row r="81" spans="3:12">
+      <c r="E81" s="136"/>
+      <c r="F81" s="137"/>
+      <c r="G81" s="138"/>
+      <c r="H81" s="139"/>
+      <c r="I81" s="140"/>
+      <c r="J81" s="140"/>
+      <c r="K81" s="140"/>
+      <c r="L81" s="52"/>
+    </row>
+    <row r="82" spans="3:12">
+      <c r="E82" s="136"/>
+      <c r="F82" s="137"/>
+      <c r="G82" s="138"/>
+      <c r="H82" s="139"/>
+      <c r="I82" s="140"/>
+      <c r="J82" s="140"/>
+      <c r="K82" s="140"/>
+      <c r="L82" s="52"/>
+    </row>
+    <row r="83" spans="3:12">
+      <c r="E83" s="136"/>
+      <c r="F83" s="137"/>
+      <c r="G83" s="138"/>
+      <c r="H83" s="139"/>
+      <c r="I83" s="136"/>
+      <c r="J83" s="140"/>
+      <c r="K83" s="140"/>
+    </row>
+    <row r="84" spans="3:12">
+      <c r="E84" s="136"/>
+      <c r="F84" s="137"/>
+      <c r="G84" s="138"/>
+      <c r="H84" s="139"/>
+      <c r="I84" s="136"/>
+      <c r="J84" s="140"/>
+      <c r="K84" s="140"/>
+    </row>
+    <row r="85" spans="3:12">
+      <c r="E85" s="136"/>
+      <c r="F85" s="137"/>
+      <c r="G85" s="138"/>
+      <c r="H85" s="139"/>
+      <c r="I85" s="136"/>
+      <c r="J85" s="140"/>
+      <c r="K85" s="140"/>
+    </row>
+    <row r="86" spans="3:12">
+      <c r="E86" s="136"/>
+      <c r="F86" s="137"/>
+      <c r="G86" s="138"/>
+      <c r="H86" s="139"/>
+      <c r="I86" s="136"/>
+      <c r="J86" s="140"/>
+      <c r="K86" s="140"/>
+    </row>
+    <row r="87" spans="3:12">
+      <c r="E87" s="136"/>
+      <c r="F87" s="137"/>
+      <c r="G87" s="138"/>
+      <c r="H87" s="139"/>
+      <c r="I87" s="136"/>
+      <c r="J87" s="140"/>
+      <c r="K87" s="140"/>
+    </row>
+    <row r="88" spans="3:12">
+      <c r="E88" s="136"/>
+      <c r="F88" s="137"/>
+      <c r="G88" s="138"/>
+      <c r="H88" s="139"/>
+      <c r="I88" s="141"/>
+      <c r="J88" s="140"/>
+      <c r="K88" s="140"/>
+    </row>
+    <row r="89" spans="3:12">
+      <c r="E89" s="136"/>
+      <c r="F89" s="137"/>
+      <c r="G89" s="138"/>
+      <c r="H89" s="139"/>
+      <c r="I89" s="141"/>
+      <c r="J89" s="140"/>
+      <c r="K89" s="140"/>
+    </row>
+    <row r="90" spans="3:12">
+      <c r="C90" s="69"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="136"/>
+      <c r="F90" s="137"/>
+      <c r="G90" s="138"/>
+      <c r="H90" s="139"/>
+      <c r="I90" s="141"/>
+      <c r="J90" s="140"/>
+      <c r="K90" s="140"/>
+    </row>
+    <row r="91" spans="3:12">
+      <c r="E91" s="136"/>
+      <c r="F91" s="137"/>
+      <c r="G91" s="138"/>
+      <c r="H91" s="139"/>
+      <c r="I91" s="141"/>
+      <c r="J91" s="140"/>
+      <c r="K91" s="140"/>
+    </row>
+    <row r="92" spans="3:12">
+      <c r="E92" s="92"/>
+      <c r="F92" s="142"/>
+      <c r="G92" s="138"/>
+      <c r="H92" s="143"/>
+      <c r="J92" s="92"/>
+      <c r="K92" s="140"/>
+    </row>
+    <row r="93" spans="3:12">
+      <c r="E93" s="92"/>
+      <c r="F93" s="142"/>
+      <c r="G93" s="138"/>
+      <c r="H93" s="144"/>
+      <c r="J93" s="92"/>
+      <c r="K93" s="140"/>
+    </row>
+    <row r="94" spans="3:12">
+      <c r="E94" s="92"/>
+      <c r="F94" s="88"/>
+      <c r="G94" s="138"/>
+      <c r="H94" s="145"/>
+      <c r="J94" s="146"/>
+      <c r="K94" s="140"/>
+      <c r="L94" s="49"/>
+    </row>
+    <row r="95" spans="3:12">
+      <c r="E95" s="92"/>
+      <c r="F95" s="88"/>
+      <c r="G95" s="138"/>
+      <c r="H95" s="145"/>
+      <c r="J95" s="146"/>
+      <c r="K95" s="140"/>
+      <c r="L95" s="49"/>
+    </row>
+    <row r="96" spans="3:12">
+      <c r="E96" s="92"/>
+      <c r="F96" s="88"/>
+      <c r="G96" s="138"/>
+      <c r="H96" s="145"/>
+      <c r="J96" s="146"/>
+      <c r="K96" s="140"/>
+      <c r="L96" s="49"/>
+    </row>
+    <row r="97" spans="5:12">
+      <c r="E97" s="92"/>
+      <c r="F97" s="88"/>
+      <c r="G97" s="138"/>
+      <c r="H97" s="145"/>
+      <c r="J97" s="146"/>
+      <c r="K97" s="140"/>
+      <c r="L97" s="49"/>
+    </row>
+    <row r="98" spans="5:12">
+      <c r="E98" s="92"/>
+      <c r="F98" s="88"/>
+      <c r="G98" s="138"/>
+      <c r="H98" s="145"/>
+      <c r="J98" s="146"/>
+      <c r="K98" s="140"/>
+      <c r="L98" s="49"/>
+    </row>
+    <row r="99" spans="5:12">
+      <c r="E99" s="92"/>
+      <c r="F99" s="88"/>
+      <c r="G99" s="138"/>
+      <c r="H99" s="145"/>
+      <c r="J99" s="146"/>
+      <c r="K99" s="140"/>
+      <c r="L99" s="49"/>
+    </row>
+    <row r="100" spans="5:12">
+      <c r="E100" s="92"/>
+      <c r="F100" s="147"/>
+      <c r="G100" s="138"/>
+      <c r="H100" s="144"/>
+      <c r="I100" s="92"/>
+      <c r="J100" s="146"/>
+      <c r="K100" s="140"/>
+    </row>
+    <row r="101" spans="5:12">
+      <c r="E101" s="92"/>
+      <c r="F101" s="147"/>
+      <c r="G101" s="138"/>
+      <c r="H101" s="144"/>
+      <c r="I101" s="92"/>
+      <c r="J101" s="146"/>
+      <c r="K101" s="140"/>
+    </row>
+    <row r="102" spans="5:12">
+      <c r="E102" s="92"/>
+      <c r="F102" s="147"/>
+      <c r="G102" s="138"/>
+      <c r="H102" s="144"/>
+      <c r="I102" s="92"/>
+      <c r="J102" s="146"/>
+      <c r="K102" s="140"/>
+    </row>
+    <row r="103" spans="5:12">
+      <c r="E103" s="92"/>
+      <c r="F103" s="92"/>
+      <c r="G103" s="138"/>
+      <c r="H103" s="92"/>
+      <c r="I103" s="92"/>
+      <c r="J103" s="92"/>
+      <c r="K103" s="92"/>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="A27:F29"/>
+    <mergeCell ref="A1:K4"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="H8:K10"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:K12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H15:K17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B31:C34"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="E31:E34"/>
+    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="G31:H34"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="K31:K34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A55:E58"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:H58"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J58"/>
+    <mergeCell ref="K55:K58"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="G52:H52"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.16" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:P112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
